--- a/report_2.xlsx
+++ b/report_2.xlsx
@@ -7320,7 +7320,7 @@
         <v>40759</v>
       </c>
       <c r="E2" t="n">
-        <v>5371</v>
+        <v>5376</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
@@ -7346,7 +7346,7 @@
         <v>40878</v>
       </c>
       <c r="E3" t="n">
-        <v>5252</v>
+        <v>5257</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
@@ -7372,7 +7372,7 @@
         <v>41152</v>
       </c>
       <c r="E4" t="n">
-        <v>4978</v>
+        <v>4983</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
@@ -7398,7 +7398,7 @@
         <v>41486</v>
       </c>
       <c r="E5" t="n">
-        <v>4644</v>
+        <v>4649</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
@@ -7424,7 +7424,7 @@
         <v>41686</v>
       </c>
       <c r="E6" t="n">
-        <v>4444</v>
+        <v>4449</v>
       </c>
       <c r="F6" t="b">
         <v>1</v>
@@ -7450,7 +7450,7 @@
         <v>41874</v>
       </c>
       <c r="E7" t="n">
-        <v>4256</v>
+        <v>4261</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
@@ -7476,7 +7476,7 @@
         <v>41947</v>
       </c>
       <c r="E8" t="n">
-        <v>4183</v>
+        <v>4188</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -7502,7 +7502,7 @@
         <v>41980</v>
       </c>
       <c r="E9" t="n">
-        <v>4150</v>
+        <v>4155</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -7528,7 +7528,7 @@
         <v>42045</v>
       </c>
       <c r="E10" t="n">
-        <v>4085</v>
+        <v>4090</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
@@ -7554,7 +7554,7 @@
         <v>42123</v>
       </c>
       <c r="E11" t="n">
-        <v>4007</v>
+        <v>4012</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
@@ -7580,7 +7580,7 @@
         <v>42139</v>
       </c>
       <c r="E12" t="n">
-        <v>3991</v>
+        <v>3996</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
@@ -7606,7 +7606,7 @@
         <v>42167</v>
       </c>
       <c r="E13" t="n">
-        <v>3963</v>
+        <v>3968</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
@@ -7632,7 +7632,7 @@
         <v>42271</v>
       </c>
       <c r="E14" t="n">
-        <v>3859</v>
+        <v>3864</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
@@ -7658,7 +7658,7 @@
         <v>42284</v>
       </c>
       <c r="E15" t="n">
-        <v>3846</v>
+        <v>3851</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -7684,7 +7684,7 @@
         <v>42298</v>
       </c>
       <c r="E16" t="n">
-        <v>3832</v>
+        <v>3837</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
@@ -7710,7 +7710,7 @@
         <v>42299</v>
       </c>
       <c r="E17" t="n">
-        <v>3831</v>
+        <v>3836</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
@@ -7736,7 +7736,7 @@
         <v>42422</v>
       </c>
       <c r="E18" t="n">
-        <v>3708</v>
+        <v>3713</v>
       </c>
       <c r="F18" t="b">
         <v>1</v>
@@ -7762,7 +7762,7 @@
         <v>42546</v>
       </c>
       <c r="E19" t="n">
-        <v>3584</v>
+        <v>3589</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
@@ -7788,7 +7788,7 @@
         <v>42565</v>
       </c>
       <c r="E20" t="n">
-        <v>3565</v>
+        <v>3570</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
@@ -7814,7 +7814,7 @@
         <v>42571</v>
       </c>
       <c r="E21" t="n">
-        <v>3559</v>
+        <v>3564</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
@@ -7840,7 +7840,7 @@
         <v>42581</v>
       </c>
       <c r="E22" t="n">
-        <v>3549</v>
+        <v>3554</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
@@ -7866,7 +7866,7 @@
         <v>42627</v>
       </c>
       <c r="E23" t="n">
-        <v>3503</v>
+        <v>3508</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
@@ -7892,7 +7892,7 @@
         <v>42649</v>
       </c>
       <c r="E24" t="n">
-        <v>3481</v>
+        <v>3486</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
@@ -7918,7 +7918,7 @@
         <v>42666</v>
       </c>
       <c r="E25" t="n">
-        <v>3464</v>
+        <v>3469</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
@@ -7944,7 +7944,7 @@
         <v>42669</v>
       </c>
       <c r="E26" t="n">
-        <v>3461</v>
+        <v>3466</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
@@ -7970,7 +7970,7 @@
         <v>42689</v>
       </c>
       <c r="E27" t="n">
-        <v>3441</v>
+        <v>3446</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
@@ -7996,7 +7996,7 @@
         <v>42720</v>
       </c>
       <c r="E28" t="n">
-        <v>3410</v>
+        <v>3415</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
@@ -8022,7 +8022,7 @@
         <v>42871</v>
       </c>
       <c r="E29" t="n">
-        <v>3259</v>
+        <v>3264</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
@@ -8048,7 +8048,7 @@
         <v>42916</v>
       </c>
       <c r="E30" t="n">
-        <v>3214</v>
+        <v>3219</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
@@ -8074,7 +8074,7 @@
         <v>42922</v>
       </c>
       <c r="E31" t="n">
-        <v>3208</v>
+        <v>3213</v>
       </c>
       <c r="F31" t="b">
         <v>1</v>
@@ -8100,7 +8100,7 @@
         <v>42927</v>
       </c>
       <c r="E32" t="n">
-        <v>3203</v>
+        <v>3208</v>
       </c>
       <c r="F32" t="b">
         <v>1</v>
@@ -8126,7 +8126,7 @@
         <v>42928</v>
       </c>
       <c r="E33" t="n">
-        <v>3202</v>
+        <v>3207</v>
       </c>
       <c r="F33" t="b">
         <v>1</v>
@@ -8152,7 +8152,7 @@
         <v>42947</v>
       </c>
       <c r="E34" t="n">
-        <v>3183</v>
+        <v>3188</v>
       </c>
       <c r="F34" t="b">
         <v>1</v>
@@ -8178,7 +8178,7 @@
         <v>42951</v>
       </c>
       <c r="E35" t="n">
-        <v>3179</v>
+        <v>3184</v>
       </c>
       <c r="F35" t="b">
         <v>1</v>
@@ -8204,7 +8204,7 @@
         <v>42963</v>
       </c>
       <c r="E36" t="n">
-        <v>3167</v>
+        <v>3172</v>
       </c>
       <c r="F36" t="b">
         <v>1</v>
@@ -8230,7 +8230,7 @@
         <v>43009</v>
       </c>
       <c r="E37" t="n">
-        <v>3121</v>
+        <v>3126</v>
       </c>
       <c r="F37" t="b">
         <v>1</v>
@@ -8256,7 +8256,7 @@
         <v>43017</v>
       </c>
       <c r="E38" t="n">
-        <v>3113</v>
+        <v>3118</v>
       </c>
       <c r="F38" t="b">
         <v>1</v>
@@ -8282,7 +8282,7 @@
         <v>43034</v>
       </c>
       <c r="E39" t="n">
-        <v>3096</v>
+        <v>3101</v>
       </c>
       <c r="F39" t="b">
         <v>1</v>
@@ -8308,7 +8308,7 @@
         <v>43042</v>
       </c>
       <c r="E40" t="n">
-        <v>3088</v>
+        <v>3093</v>
       </c>
       <c r="F40" t="b">
         <v>1</v>
@@ -8334,7 +8334,7 @@
         <v>43093</v>
       </c>
       <c r="E41" t="n">
-        <v>3037</v>
+        <v>3042</v>
       </c>
       <c r="F41" t="b">
         <v>1</v>
@@ -8360,7 +8360,7 @@
         <v>43102</v>
       </c>
       <c r="E42" t="n">
-        <v>3028</v>
+        <v>3033</v>
       </c>
       <c r="F42" t="b">
         <v>1</v>
@@ -8386,7 +8386,7 @@
         <v>43171</v>
       </c>
       <c r="E43" t="n">
-        <v>2959</v>
+        <v>2964</v>
       </c>
       <c r="F43" t="b">
         <v>1</v>
@@ -8412,7 +8412,7 @@
         <v>43201</v>
       </c>
       <c r="E44" t="n">
-        <v>2929</v>
+        <v>2934</v>
       </c>
       <c r="F44" t="b">
         <v>1</v>
@@ -8438,7 +8438,7 @@
         <v>43203</v>
       </c>
       <c r="E45" t="n">
-        <v>2927</v>
+        <v>2932</v>
       </c>
       <c r="F45" t="b">
         <v>1</v>
@@ -8464,7 +8464,7 @@
         <v>43217</v>
       </c>
       <c r="E46" t="n">
-        <v>2913</v>
+        <v>2918</v>
       </c>
       <c r="F46" t="b">
         <v>1</v>
@@ -8490,7 +8490,7 @@
         <v>43297</v>
       </c>
       <c r="E47" t="n">
-        <v>2833</v>
+        <v>2838</v>
       </c>
       <c r="F47" t="b">
         <v>1</v>
@@ -8516,7 +8516,7 @@
         <v>43299</v>
       </c>
       <c r="E48" t="n">
-        <v>2831</v>
+        <v>2836</v>
       </c>
       <c r="F48" t="b">
         <v>1</v>
@@ -8542,7 +8542,7 @@
         <v>43336</v>
       </c>
       <c r="E49" t="n">
-        <v>2794</v>
+        <v>2799</v>
       </c>
       <c r="F49" t="b">
         <v>1</v>
@@ -8568,7 +8568,7 @@
         <v>43354</v>
       </c>
       <c r="E50" t="n">
-        <v>2776</v>
+        <v>2781</v>
       </c>
       <c r="F50" t="b">
         <v>1</v>
@@ -8594,7 +8594,7 @@
         <v>43376</v>
       </c>
       <c r="E51" t="n">
-        <v>2754</v>
+        <v>2759</v>
       </c>
       <c r="F51" t="b">
         <v>1</v>
@@ -8620,7 +8620,7 @@
         <v>43409</v>
       </c>
       <c r="E52" t="n">
-        <v>2721</v>
+        <v>2726</v>
       </c>
       <c r="F52" t="b">
         <v>1</v>
@@ -8646,7 +8646,7 @@
         <v>43518</v>
       </c>
       <c r="E53" t="n">
-        <v>2612</v>
+        <v>2617</v>
       </c>
       <c r="F53" t="b">
         <v>1</v>
@@ -8672,7 +8672,7 @@
         <v>43541</v>
       </c>
       <c r="E54" t="n">
-        <v>2589</v>
+        <v>2594</v>
       </c>
       <c r="F54" t="b">
         <v>1</v>
@@ -8698,7 +8698,7 @@
         <v>43560</v>
       </c>
       <c r="E55" t="n">
-        <v>2570</v>
+        <v>2575</v>
       </c>
       <c r="F55" t="b">
         <v>1</v>
@@ -8724,7 +8724,7 @@
         <v>43591</v>
       </c>
       <c r="E56" t="n">
-        <v>2539</v>
+        <v>2544</v>
       </c>
       <c r="F56" t="b">
         <v>1</v>
@@ -8750,7 +8750,7 @@
         <v>43611</v>
       </c>
       <c r="E57" t="n">
-        <v>2519</v>
+        <v>2524</v>
       </c>
       <c r="F57" t="b">
         <v>1</v>
@@ -8776,7 +8776,7 @@
         <v>43619</v>
       </c>
       <c r="E58" t="n">
-        <v>2511</v>
+        <v>2516</v>
       </c>
       <c r="F58" t="b">
         <v>1</v>
@@ -8802,7 +8802,7 @@
         <v>43666</v>
       </c>
       <c r="E59" t="n">
-        <v>2464</v>
+        <v>2469</v>
       </c>
       <c r="F59" t="b">
         <v>1</v>
@@ -8828,7 +8828,7 @@
         <v>43680</v>
       </c>
       <c r="E60" t="n">
-        <v>2450</v>
+        <v>2455</v>
       </c>
       <c r="F60" t="b">
         <v>1</v>
@@ -8854,7 +8854,7 @@
         <v>43704</v>
       </c>
       <c r="E61" t="n">
-        <v>2426</v>
+        <v>2431</v>
       </c>
       <c r="F61" t="b">
         <v>1</v>
@@ -8880,7 +8880,7 @@
         <v>43747</v>
       </c>
       <c r="E62" t="n">
-        <v>2383</v>
+        <v>2388</v>
       </c>
       <c r="F62" t="b">
         <v>1</v>
@@ -8906,7 +8906,7 @@
         <v>43780</v>
       </c>
       <c r="E63" t="n">
-        <v>2350</v>
+        <v>2355</v>
       </c>
       <c r="F63" t="b">
         <v>1</v>
@@ -8932,7 +8932,7 @@
         <v>43792</v>
       </c>
       <c r="E64" t="n">
-        <v>2338</v>
+        <v>2343</v>
       </c>
       <c r="F64" t="b">
         <v>1</v>
@@ -8958,7 +8958,7 @@
         <v>43796</v>
       </c>
       <c r="E65" t="n">
-        <v>2334</v>
+        <v>2339</v>
       </c>
       <c r="F65" t="b">
         <v>1</v>
@@ -8984,7 +8984,7 @@
         <v>43811</v>
       </c>
       <c r="E66" t="n">
-        <v>2319</v>
+        <v>2324</v>
       </c>
       <c r="F66" t="b">
         <v>1</v>
@@ -9010,7 +9010,7 @@
         <v>43960</v>
       </c>
       <c r="E67" t="n">
-        <v>2170</v>
+        <v>2175</v>
       </c>
       <c r="F67" t="b">
         <v>1</v>
@@ -9036,7 +9036,7 @@
         <v>43969</v>
       </c>
       <c r="E68" t="n">
-        <v>2161</v>
+        <v>2166</v>
       </c>
       <c r="F68" t="b">
         <v>1</v>
@@ -9062,7 +9062,7 @@
         <v>43996</v>
       </c>
       <c r="E69" t="n">
-        <v>2134</v>
+        <v>2139</v>
       </c>
       <c r="F69" t="b">
         <v>1</v>
@@ -9071,24 +9071,24 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>D203234</t>
+          <t>D205927</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Clinic_234</t>
+          <t>Clinic_646</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D70" s="1" t="n">
         <v>43997</v>
       </c>
       <c r="E70" t="n">
-        <v>2133</v>
+        <v>2138</v>
       </c>
       <c r="F70" t="b">
         <v>1</v>
@@ -9097,24 +9097,24 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>D205927</t>
+          <t>D203234</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Clinic_646</t>
+          <t>Clinic_234</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D71" s="1" t="n">
         <v>43997</v>
       </c>
       <c r="E71" t="n">
-        <v>2133</v>
+        <v>2138</v>
       </c>
       <c r="F71" t="b">
         <v>1</v>
@@ -9140,7 +9140,7 @@
         <v>44024</v>
       </c>
       <c r="E72" t="n">
-        <v>2106</v>
+        <v>2111</v>
       </c>
       <c r="F72" t="b">
         <v>1</v>
@@ -9166,7 +9166,7 @@
         <v>44035</v>
       </c>
       <c r="E73" t="n">
-        <v>2095</v>
+        <v>2100</v>
       </c>
       <c r="F73" t="b">
         <v>1</v>
@@ -9192,7 +9192,7 @@
         <v>44041</v>
       </c>
       <c r="E74" t="n">
-        <v>2089</v>
+        <v>2094</v>
       </c>
       <c r="F74" t="b">
         <v>1</v>
@@ -9218,7 +9218,7 @@
         <v>44053</v>
       </c>
       <c r="E75" t="n">
-        <v>2077</v>
+        <v>2082</v>
       </c>
       <c r="F75" t="b">
         <v>1</v>
@@ -9244,7 +9244,7 @@
         <v>44063</v>
       </c>
       <c r="E76" t="n">
-        <v>2067</v>
+        <v>2072</v>
       </c>
       <c r="F76" t="b">
         <v>1</v>
@@ -9270,7 +9270,7 @@
         <v>44107</v>
       </c>
       <c r="E77" t="n">
-        <v>2023</v>
+        <v>2028</v>
       </c>
       <c r="F77" t="b">
         <v>1</v>
@@ -9296,7 +9296,7 @@
         <v>44108</v>
       </c>
       <c r="E78" t="n">
-        <v>2022</v>
+        <v>2027</v>
       </c>
       <c r="F78" t="b">
         <v>1</v>
@@ -9322,7 +9322,7 @@
         <v>44143</v>
       </c>
       <c r="E79" t="n">
-        <v>1987</v>
+        <v>1992</v>
       </c>
       <c r="F79" t="b">
         <v>1</v>
@@ -9348,7 +9348,7 @@
         <v>44178</v>
       </c>
       <c r="E80" t="n">
-        <v>1952</v>
+        <v>1957</v>
       </c>
       <c r="F80" t="b">
         <v>1</v>
@@ -9374,7 +9374,7 @@
         <v>44198</v>
       </c>
       <c r="E81" t="n">
-        <v>1932</v>
+        <v>1937</v>
       </c>
       <c r="F81" t="b">
         <v>1</v>
@@ -9400,7 +9400,7 @@
         <v>44256</v>
       </c>
       <c r="E82" t="n">
-        <v>1874</v>
+        <v>1879</v>
       </c>
       <c r="F82" t="b">
         <v>1</v>
@@ -9426,7 +9426,7 @@
         <v>44268</v>
       </c>
       <c r="E83" t="n">
-        <v>1862</v>
+        <v>1867</v>
       </c>
       <c r="F83" t="b">
         <v>1</v>
@@ -9452,7 +9452,7 @@
         <v>44276</v>
       </c>
       <c r="E84" t="n">
-        <v>1854</v>
+        <v>1859</v>
       </c>
       <c r="F84" t="b">
         <v>1</v>
@@ -9478,7 +9478,7 @@
         <v>44287</v>
       </c>
       <c r="E85" t="n">
-        <v>1843</v>
+        <v>1848</v>
       </c>
       <c r="F85" t="b">
         <v>1</v>
@@ -9504,7 +9504,7 @@
         <v>44301</v>
       </c>
       <c r="E86" t="n">
-        <v>1829</v>
+        <v>1834</v>
       </c>
       <c r="F86" t="b">
         <v>1</v>
@@ -9530,7 +9530,7 @@
         <v>44323</v>
       </c>
       <c r="E87" t="n">
-        <v>1807</v>
+        <v>1812</v>
       </c>
       <c r="F87" t="b">
         <v>1</v>
@@ -9556,7 +9556,7 @@
         <v>44324</v>
       </c>
       <c r="E88" t="n">
-        <v>1806</v>
+        <v>1811</v>
       </c>
       <c r="F88" t="b">
         <v>1</v>
@@ -9582,7 +9582,7 @@
         <v>44366</v>
       </c>
       <c r="E89" t="n">
-        <v>1764</v>
+        <v>1769</v>
       </c>
       <c r="F89" t="b">
         <v>1</v>
@@ -9608,7 +9608,7 @@
         <v>44424</v>
       </c>
       <c r="E90" t="n">
-        <v>1706</v>
+        <v>1711</v>
       </c>
       <c r="F90" t="b">
         <v>1</v>
@@ -9634,7 +9634,7 @@
         <v>44425</v>
       </c>
       <c r="E91" t="n">
-        <v>1705</v>
+        <v>1710</v>
       </c>
       <c r="F91" t="b">
         <v>1</v>
@@ -9660,7 +9660,7 @@
         <v>44430</v>
       </c>
       <c r="E92" t="n">
-        <v>1700</v>
+        <v>1705</v>
       </c>
       <c r="F92" t="b">
         <v>1</v>
@@ -9686,7 +9686,7 @@
         <v>44432</v>
       </c>
       <c r="E93" t="n">
-        <v>1698</v>
+        <v>1703</v>
       </c>
       <c r="F93" t="b">
         <v>1</v>
@@ -9712,7 +9712,7 @@
         <v>44441</v>
       </c>
       <c r="E94" t="n">
-        <v>1689</v>
+        <v>1694</v>
       </c>
       <c r="F94" t="b">
         <v>1</v>
@@ -9738,7 +9738,7 @@
         <v>44516</v>
       </c>
       <c r="E95" t="n">
-        <v>1614</v>
+        <v>1619</v>
       </c>
       <c r="F95" t="b">
         <v>1</v>
@@ -9764,7 +9764,7 @@
         <v>44518</v>
       </c>
       <c r="E96" t="n">
-        <v>1612</v>
+        <v>1617</v>
       </c>
       <c r="F96" t="b">
         <v>1</v>
@@ -9790,7 +9790,7 @@
         <v>44547</v>
       </c>
       <c r="E97" t="n">
-        <v>1583</v>
+        <v>1588</v>
       </c>
       <c r="F97" t="b">
         <v>1</v>
@@ -9816,7 +9816,7 @@
         <v>44548</v>
       </c>
       <c r="E98" t="n">
-        <v>1582</v>
+        <v>1587</v>
       </c>
       <c r="F98" t="b">
         <v>1</v>
@@ -9842,7 +9842,7 @@
         <v>44596</v>
       </c>
       <c r="E99" t="n">
-        <v>1534</v>
+        <v>1539</v>
       </c>
       <c r="F99" t="b">
         <v>1</v>
@@ -9868,7 +9868,7 @@
         <v>44604</v>
       </c>
       <c r="E100" t="n">
-        <v>1526</v>
+        <v>1531</v>
       </c>
       <c r="F100" t="b">
         <v>1</v>
@@ -9894,7 +9894,7 @@
         <v>44607</v>
       </c>
       <c r="E101" t="n">
-        <v>1523</v>
+        <v>1528</v>
       </c>
       <c r="F101" t="b">
         <v>1</v>
@@ -9920,7 +9920,7 @@
         <v>44643</v>
       </c>
       <c r="E102" t="n">
-        <v>1487</v>
+        <v>1492</v>
       </c>
       <c r="F102" t="b">
         <v>1</v>
@@ -9946,7 +9946,7 @@
         <v>44659</v>
       </c>
       <c r="E103" t="n">
-        <v>1471</v>
+        <v>1476</v>
       </c>
       <c r="F103" t="b">
         <v>1</v>
@@ -9972,7 +9972,7 @@
         <v>44673</v>
       </c>
       <c r="E104" t="n">
-        <v>1457</v>
+        <v>1462</v>
       </c>
       <c r="F104" t="b">
         <v>1</v>
@@ -9998,7 +9998,7 @@
         <v>44704</v>
       </c>
       <c r="E105" t="n">
-        <v>1426</v>
+        <v>1431</v>
       </c>
       <c r="F105" t="b">
         <v>1</v>
@@ -10024,7 +10024,7 @@
         <v>44706</v>
       </c>
       <c r="E106" t="n">
-        <v>1424</v>
+        <v>1429</v>
       </c>
       <c r="F106" t="b">
         <v>1</v>
@@ -10050,7 +10050,7 @@
         <v>44711</v>
       </c>
       <c r="E107" t="n">
-        <v>1419</v>
+        <v>1424</v>
       </c>
       <c r="F107" t="b">
         <v>1</v>
@@ -10076,7 +10076,7 @@
         <v>44718</v>
       </c>
       <c r="E108" t="n">
-        <v>1412</v>
+        <v>1417</v>
       </c>
       <c r="F108" t="b">
         <v>1</v>
@@ -10102,7 +10102,7 @@
         <v>44719</v>
       </c>
       <c r="E109" t="n">
-        <v>1411</v>
+        <v>1416</v>
       </c>
       <c r="F109" t="b">
         <v>1</v>
@@ -10128,7 +10128,7 @@
         <v>44721</v>
       </c>
       <c r="E110" t="n">
-        <v>1409</v>
+        <v>1414</v>
       </c>
       <c r="F110" t="b">
         <v>1</v>
@@ -10154,7 +10154,7 @@
         <v>44731</v>
       </c>
       <c r="E111" t="n">
-        <v>1399</v>
+        <v>1404</v>
       </c>
       <c r="F111" t="b">
         <v>1</v>
@@ -10180,7 +10180,7 @@
         <v>44735</v>
       </c>
       <c r="E112" t="n">
-        <v>1395</v>
+        <v>1400</v>
       </c>
       <c r="F112" t="b">
         <v>1</v>
@@ -10206,7 +10206,7 @@
         <v>44756</v>
       </c>
       <c r="E113" t="n">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="F113" t="b">
         <v>1</v>
@@ -10232,7 +10232,7 @@
         <v>44781</v>
       </c>
       <c r="E114" t="n">
-        <v>1349</v>
+        <v>1354</v>
       </c>
       <c r="F114" t="b">
         <v>1</v>
@@ -10258,7 +10258,7 @@
         <v>44793</v>
       </c>
       <c r="E115" t="n">
-        <v>1337</v>
+        <v>1342</v>
       </c>
       <c r="F115" t="b">
         <v>1</v>
@@ -10284,7 +10284,7 @@
         <v>44798</v>
       </c>
       <c r="E116" t="n">
-        <v>1332</v>
+        <v>1337</v>
       </c>
       <c r="F116" t="b">
         <v>1</v>
@@ -10310,7 +10310,7 @@
         <v>44807</v>
       </c>
       <c r="E117" t="n">
-        <v>1323</v>
+        <v>1328</v>
       </c>
       <c r="F117" t="b">
         <v>1</v>
@@ -10336,7 +10336,7 @@
         <v>44810</v>
       </c>
       <c r="E118" t="n">
-        <v>1320</v>
+        <v>1325</v>
       </c>
       <c r="F118" t="b">
         <v>1</v>
@@ -10362,7 +10362,7 @@
         <v>44821</v>
       </c>
       <c r="E119" t="n">
-        <v>1309</v>
+        <v>1314</v>
       </c>
       <c r="F119" t="b">
         <v>1</v>
@@ -10388,7 +10388,7 @@
         <v>44898</v>
       </c>
       <c r="E120" t="n">
-        <v>1232</v>
+        <v>1237</v>
       </c>
       <c r="F120" t="b">
         <v>1</v>
@@ -10414,7 +10414,7 @@
         <v>44901</v>
       </c>
       <c r="E121" t="n">
-        <v>1229</v>
+        <v>1234</v>
       </c>
       <c r="F121" t="b">
         <v>1</v>
@@ -10440,7 +10440,7 @@
         <v>44903</v>
       </c>
       <c r="E122" t="n">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="F122" t="b">
         <v>1</v>
@@ -10466,7 +10466,7 @@
         <v>44919</v>
       </c>
       <c r="E123" t="n">
-        <v>1211</v>
+        <v>1216</v>
       </c>
       <c r="F123" t="b">
         <v>1</v>
@@ -10492,7 +10492,7 @@
         <v>44922</v>
       </c>
       <c r="E124" t="n">
-        <v>1208</v>
+        <v>1213</v>
       </c>
       <c r="F124" t="b">
         <v>1</v>
@@ -10518,7 +10518,7 @@
         <v>44937</v>
       </c>
       <c r="E125" t="n">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="F125" t="b">
         <v>1</v>
@@ -10544,7 +10544,7 @@
         <v>44953</v>
       </c>
       <c r="E126" t="n">
-        <v>1177</v>
+        <v>1182</v>
       </c>
       <c r="F126" t="b">
         <v>1</v>
@@ -10570,7 +10570,7 @@
         <v>44954</v>
       </c>
       <c r="E127" t="n">
-        <v>1176</v>
+        <v>1181</v>
       </c>
       <c r="F127" t="b">
         <v>1</v>
@@ -10596,7 +10596,7 @@
         <v>44958</v>
       </c>
       <c r="E128" t="n">
-        <v>1172</v>
+        <v>1177</v>
       </c>
       <c r="F128" t="b">
         <v>1</v>
@@ -10622,7 +10622,7 @@
         <v>44969</v>
       </c>
       <c r="E129" t="n">
-        <v>1161</v>
+        <v>1166</v>
       </c>
       <c r="F129" t="b">
         <v>1</v>
@@ -10648,7 +10648,7 @@
         <v>44988</v>
       </c>
       <c r="E130" t="n">
-        <v>1142</v>
+        <v>1147</v>
       </c>
       <c r="F130" t="b">
         <v>1</v>
@@ -10674,7 +10674,7 @@
         <v>44992</v>
       </c>
       <c r="E131" t="n">
-        <v>1138</v>
+        <v>1143</v>
       </c>
       <c r="F131" t="b">
         <v>1</v>
@@ -10700,7 +10700,7 @@
         <v>44995</v>
       </c>
       <c r="E132" t="n">
-        <v>1135</v>
+        <v>1140</v>
       </c>
       <c r="F132" t="b">
         <v>1</v>
@@ -10726,7 +10726,7 @@
         <v>45010</v>
       </c>
       <c r="E133" t="n">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="F133" t="b">
         <v>1</v>
@@ -10752,7 +10752,7 @@
         <v>45016</v>
       </c>
       <c r="E134" t="n">
-        <v>1114</v>
+        <v>1119</v>
       </c>
       <c r="F134" t="b">
         <v>1</v>
@@ -10778,7 +10778,7 @@
         <v>45055</v>
       </c>
       <c r="E135" t="n">
-        <v>1075</v>
+        <v>1080</v>
       </c>
       <c r="F135" t="b">
         <v>1</v>
@@ -10804,7 +10804,7 @@
         <v>45064</v>
       </c>
       <c r="E136" t="n">
-        <v>1066</v>
+        <v>1071</v>
       </c>
       <c r="F136" t="b">
         <v>1</v>
@@ -10830,7 +10830,7 @@
         <v>45069</v>
       </c>
       <c r="E137" t="n">
-        <v>1061</v>
+        <v>1066</v>
       </c>
       <c r="F137" t="b">
         <v>1</v>
@@ -10856,7 +10856,7 @@
         <v>45078</v>
       </c>
       <c r="E138" t="n">
-        <v>1052</v>
+        <v>1057</v>
       </c>
       <c r="F138" t="b">
         <v>1</v>
@@ -10882,7 +10882,7 @@
         <v>45081</v>
       </c>
       <c r="E139" t="n">
-        <v>1049</v>
+        <v>1054</v>
       </c>
       <c r="F139" t="b">
         <v>1</v>
@@ -10908,7 +10908,7 @@
         <v>45085</v>
       </c>
       <c r="E140" t="n">
-        <v>1045</v>
+        <v>1050</v>
       </c>
       <c r="F140" t="b">
         <v>1</v>
@@ -10934,7 +10934,7 @@
         <v>45137</v>
       </c>
       <c r="E141" t="n">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="F141" t="b">
         <v>1</v>
@@ -10960,7 +10960,7 @@
         <v>45174</v>
       </c>
       <c r="E142" t="n">
-        <v>956</v>
+        <v>961</v>
       </c>
       <c r="F142" t="b">
         <v>1</v>
@@ -10986,7 +10986,7 @@
         <v>45180</v>
       </c>
       <c r="E143" t="n">
-        <v>950</v>
+        <v>955</v>
       </c>
       <c r="F143" t="b">
         <v>1</v>
@@ -11012,7 +11012,7 @@
         <v>45225</v>
       </c>
       <c r="E144" t="n">
-        <v>905</v>
+        <v>910</v>
       </c>
       <c r="F144" t="b">
         <v>1</v>
@@ -11038,7 +11038,7 @@
         <v>45227</v>
       </c>
       <c r="E145" t="n">
-        <v>903</v>
+        <v>908</v>
       </c>
       <c r="F145" t="b">
         <v>1</v>
@@ -11064,7 +11064,7 @@
         <v>45232</v>
       </c>
       <c r="E146" t="n">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="F146" t="b">
         <v>1</v>
@@ -11090,7 +11090,7 @@
         <v>45247</v>
       </c>
       <c r="E147" t="n">
-        <v>883</v>
+        <v>888</v>
       </c>
       <c r="F147" t="b">
         <v>1</v>
@@ -11116,7 +11116,7 @@
         <v>45252</v>
       </c>
       <c r="E148" t="n">
-        <v>878</v>
+        <v>883</v>
       </c>
       <c r="F148" t="b">
         <v>1</v>
@@ -11142,7 +11142,7 @@
         <v>45262</v>
       </c>
       <c r="E149" t="n">
-        <v>868</v>
+        <v>873</v>
       </c>
       <c r="F149" t="b">
         <v>1</v>
@@ -11168,7 +11168,7 @@
         <v>45264</v>
       </c>
       <c r="E150" t="n">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="F150" t="b">
         <v>1</v>
@@ -11194,7 +11194,7 @@
         <v>45266</v>
       </c>
       <c r="E151" t="n">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="F151" t="b">
         <v>1</v>
@@ -11220,7 +11220,7 @@
         <v>45267</v>
       </c>
       <c r="E152" t="n">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="F152" t="b">
         <v>1</v>
@@ -11246,7 +11246,7 @@
         <v>45287</v>
       </c>
       <c r="E153" t="n">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="F153" t="b">
         <v>1</v>
@@ -11255,24 +11255,24 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>D203231</t>
+          <t>D206383</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Clinic_401</t>
+          <t>Clinic_806</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="E154" t="n">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="F154" t="b">
         <v>1</v>
@@ -11281,24 +11281,24 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>D206383</t>
+          <t>D203231</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Clinic_806</t>
+          <t>Clinic_401</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D155" s="1" t="n">
         <v>45322</v>
       </c>
       <c r="E155" t="n">
-        <v>808</v>
+        <v>813</v>
       </c>
       <c r="F155" t="b">
         <v>1</v>
@@ -11324,7 +11324,7 @@
         <v>45326</v>
       </c>
       <c r="E156" t="n">
-        <v>804</v>
+        <v>809</v>
       </c>
       <c r="F156" t="b">
         <v>1</v>
@@ -11350,7 +11350,7 @@
         <v>45332</v>
       </c>
       <c r="E157" t="n">
-        <v>798</v>
+        <v>803</v>
       </c>
       <c r="F157" t="b">
         <v>1</v>
@@ -11376,7 +11376,7 @@
         <v>45334</v>
       </c>
       <c r="E158" t="n">
-        <v>796</v>
+        <v>801</v>
       </c>
       <c r="F158" t="b">
         <v>1</v>
@@ -11402,7 +11402,7 @@
         <v>45360</v>
       </c>
       <c r="E159" t="n">
-        <v>770</v>
+        <v>775</v>
       </c>
       <c r="F159" t="b">
         <v>1</v>
@@ -11411,24 +11411,24 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>D209287</t>
+          <t>D206191</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Clinic_464</t>
+          <t>Clinic_537</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D160" s="1" t="n">
         <v>45363</v>
       </c>
       <c r="E160" t="n">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="F160" t="b">
         <v>1</v>
@@ -11437,24 +11437,24 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>D206191</t>
+          <t>D209287</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Clinic_537</t>
+          <t>Clinic_464</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D161" s="1" t="n">
         <v>45363</v>
       </c>
       <c r="E161" t="n">
-        <v>767</v>
+        <v>772</v>
       </c>
       <c r="F161" t="b">
         <v>1</v>
@@ -11480,7 +11480,7 @@
         <v>45365</v>
       </c>
       <c r="E162" t="n">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="F162" t="b">
         <v>1</v>
@@ -11506,7 +11506,7 @@
         <v>45375</v>
       </c>
       <c r="E163" t="n">
-        <v>755</v>
+        <v>760</v>
       </c>
       <c r="F163" t="b">
         <v>1</v>
@@ -11515,24 +11515,24 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>D205801</t>
+          <t>D208390</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Clinic_414</t>
+          <t>Clinic_742</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D164" s="1" t="n">
         <v>45391</v>
       </c>
       <c r="E164" t="n">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F164" t="b">
         <v>1</v>
@@ -11541,24 +11541,24 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>D208390</t>
+          <t>D205801</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Clinic_742</t>
+          <t>Clinic_414</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D165" s="1" t="n">
         <v>45391</v>
       </c>
       <c r="E165" t="n">
-        <v>739</v>
+        <v>744</v>
       </c>
       <c r="F165" t="b">
         <v>1</v>
@@ -11584,7 +11584,7 @@
         <v>45395</v>
       </c>
       <c r="E166" t="n">
-        <v>735</v>
+        <v>740</v>
       </c>
       <c r="F166" t="b">
         <v>1</v>
@@ -11610,7 +11610,7 @@
         <v>45399</v>
       </c>
       <c r="E167" t="n">
-        <v>731</v>
+        <v>736</v>
       </c>
       <c r="F167" t="b">
         <v>1</v>
@@ -11636,7 +11636,7 @@
         <v>45407</v>
       </c>
       <c r="E168" t="n">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="F168" t="b">
         <v>1</v>
@@ -11662,7 +11662,7 @@
         <v>45460</v>
       </c>
       <c r="E169" t="n">
-        <v>670</v>
+        <v>675</v>
       </c>
       <c r="F169" t="b">
         <v>1</v>
@@ -11688,7 +11688,7 @@
         <v>45462</v>
       </c>
       <c r="E170" t="n">
-        <v>668</v>
+        <v>673</v>
       </c>
       <c r="F170" t="b">
         <v>1</v>
@@ -11714,7 +11714,7 @@
         <v>45473</v>
       </c>
       <c r="E171" t="n">
-        <v>657</v>
+        <v>662</v>
       </c>
       <c r="F171" t="b">
         <v>1</v>
@@ -11740,7 +11740,7 @@
         <v>45481</v>
       </c>
       <c r="E172" t="n">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="F172" t="b">
         <v>1</v>
@@ -11766,7 +11766,7 @@
         <v>45491</v>
       </c>
       <c r="E173" t="n">
-        <v>639</v>
+        <v>644</v>
       </c>
       <c r="F173" t="b">
         <v>1</v>
@@ -11792,7 +11792,7 @@
         <v>45492</v>
       </c>
       <c r="E174" t="n">
-        <v>638</v>
+        <v>643</v>
       </c>
       <c r="F174" t="b">
         <v>1</v>
@@ -11818,7 +11818,7 @@
         <v>45495</v>
       </c>
       <c r="E175" t="n">
-        <v>635</v>
+        <v>640</v>
       </c>
       <c r="F175" t="b">
         <v>1</v>
@@ -11844,7 +11844,7 @@
         <v>45506</v>
       </c>
       <c r="E176" t="n">
-        <v>624</v>
+        <v>629</v>
       </c>
       <c r="F176" t="b">
         <v>1</v>
@@ -11870,7 +11870,7 @@
         <v>45526</v>
       </c>
       <c r="E177" t="n">
-        <v>604</v>
+        <v>609</v>
       </c>
       <c r="F177" t="b">
         <v>1</v>
@@ -11896,7 +11896,7 @@
         <v>45541</v>
       </c>
       <c r="E178" t="n">
-        <v>589</v>
+        <v>594</v>
       </c>
       <c r="F178" t="b">
         <v>1</v>
@@ -11922,7 +11922,7 @@
         <v>45552</v>
       </c>
       <c r="E179" t="n">
-        <v>578</v>
+        <v>583</v>
       </c>
       <c r="F179" t="b">
         <v>1</v>
@@ -11948,7 +11948,7 @@
         <v>45559</v>
       </c>
       <c r="E180" t="n">
-        <v>571</v>
+        <v>576</v>
       </c>
       <c r="F180" t="b">
         <v>1</v>
@@ -11974,7 +11974,7 @@
         <v>45564</v>
       </c>
       <c r="E181" t="n">
-        <v>566</v>
+        <v>571</v>
       </c>
       <c r="F181" t="b">
         <v>1</v>
@@ -12000,7 +12000,7 @@
         <v>45594</v>
       </c>
       <c r="E182" t="n">
-        <v>536</v>
+        <v>541</v>
       </c>
       <c r="F182" t="b">
         <v>1</v>
@@ -12026,7 +12026,7 @@
         <v>45604</v>
       </c>
       <c r="E183" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="F183" t="b">
         <v>1</v>
@@ -12052,7 +12052,7 @@
         <v>45611</v>
       </c>
       <c r="E184" t="n">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="F184" t="b">
         <v>1</v>
@@ -12078,7 +12078,7 @@
         <v>45626</v>
       </c>
       <c r="E185" t="n">
-        <v>504</v>
+        <v>509</v>
       </c>
       <c r="F185" t="b">
         <v>1</v>
@@ -12104,7 +12104,7 @@
         <v>45632</v>
       </c>
       <c r="E186" t="n">
-        <v>498</v>
+        <v>503</v>
       </c>
       <c r="F186" t="b">
         <v>1</v>
@@ -12130,7 +12130,7 @@
         <v>45634</v>
       </c>
       <c r="E187" t="n">
-        <v>496</v>
+        <v>501</v>
       </c>
       <c r="F187" t="b">
         <v>1</v>
@@ -12156,7 +12156,7 @@
         <v>45639</v>
       </c>
       <c r="E188" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F188" t="b">
         <v>1</v>
@@ -12182,7 +12182,7 @@
         <v>45642</v>
       </c>
       <c r="E189" t="n">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="F189" t="b">
         <v>1</v>
@@ -12208,7 +12208,7 @@
         <v>45657</v>
       </c>
       <c r="E190" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="F190" t="b">
         <v>1</v>
@@ -12234,7 +12234,7 @@
         <v>45659</v>
       </c>
       <c r="E191" t="n">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F191" t="b">
         <v>1</v>
@@ -12260,7 +12260,7 @@
         <v>45672</v>
       </c>
       <c r="E192" t="n">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="F192" t="b">
         <v>1</v>
@@ -12286,7 +12286,7 @@
         <v>45675</v>
       </c>
       <c r="E193" t="n">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="F193" t="b">
         <v>1</v>
@@ -12312,7 +12312,7 @@
         <v>45679</v>
       </c>
       <c r="E194" t="n">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F194" t="b">
         <v>1</v>
@@ -12338,7 +12338,7 @@
         <v>45700</v>
       </c>
       <c r="E195" t="n">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="F195" t="b">
         <v>1</v>
@@ -12364,7 +12364,7 @@
         <v>45713</v>
       </c>
       <c r="E196" t="n">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F196" t="b">
         <v>1</v>
@@ -12390,7 +12390,7 @@
         <v>45715</v>
       </c>
       <c r="E197" t="n">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="F197" t="b">
         <v>1</v>
@@ -12416,7 +12416,7 @@
         <v>45728</v>
       </c>
       <c r="E198" t="n">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="F198" t="b">
         <v>1</v>
@@ -12442,7 +12442,7 @@
         <v>45730</v>
       </c>
       <c r="E199" t="n">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="F199" t="b">
         <v>1</v>
@@ -12468,7 +12468,7 @@
         <v>45732</v>
       </c>
       <c r="E200" t="n">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="F200" t="b">
         <v>1</v>
@@ -12477,24 +12477,24 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>D203626</t>
+          <t>D208757</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Clinic_841</t>
+          <t>Clinic_561</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D201" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="E201" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F201" t="b">
         <v>1</v>
@@ -12503,24 +12503,24 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>D208757</t>
+          <t>D203626</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Clinic_561</t>
+          <t>Clinic_841</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
         <v>45737</v>
       </c>
       <c r="E202" t="n">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="F202" t="b">
         <v>1</v>
@@ -12546,7 +12546,7 @@
         <v>45743</v>
       </c>
       <c r="E203" t="n">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="F203" t="b">
         <v>1</v>
@@ -12572,10 +12572,10 @@
         <v>45766</v>
       </c>
       <c r="E204" t="n">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="F204" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -12598,7 +12598,7 @@
         <v>45773</v>
       </c>
       <c r="E205" t="n">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F205" t="b">
         <v>0</v>
@@ -12624,7 +12624,7 @@
         <v>45775</v>
       </c>
       <c r="E206" t="n">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F206" t="b">
         <v>0</v>
@@ -12650,7 +12650,7 @@
         <v>45785</v>
       </c>
       <c r="E207" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F207" t="b">
         <v>0</v>
@@ -12676,7 +12676,7 @@
         <v>45785</v>
       </c>
       <c r="E208" t="n">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F208" t="b">
         <v>0</v>
@@ -12702,7 +12702,7 @@
         <v>45803</v>
       </c>
       <c r="E209" t="n">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F209" t="b">
         <v>0</v>
@@ -12728,7 +12728,7 @@
         <v>45805</v>
       </c>
       <c r="E210" t="n">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="F210" t="b">
         <v>0</v>
@@ -12754,7 +12754,7 @@
         <v>45812</v>
       </c>
       <c r="E211" t="n">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F211" t="b">
         <v>0</v>
@@ -12780,7 +12780,7 @@
         <v>45826</v>
       </c>
       <c r="E212" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F212" t="b">
         <v>0</v>
@@ -12806,7 +12806,7 @@
         <v>45826</v>
       </c>
       <c r="E213" t="n">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="F213" t="b">
         <v>0</v>
@@ -12832,7 +12832,7 @@
         <v>45838</v>
       </c>
       <c r="E214" t="n">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F214" t="b">
         <v>0</v>
@@ -12858,7 +12858,7 @@
         <v>45848</v>
       </c>
       <c r="E215" t="n">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F215" t="b">
         <v>0</v>
@@ -12884,7 +12884,7 @@
         <v>45852</v>
       </c>
       <c r="E216" t="n">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="F216" t="b">
         <v>0</v>
@@ -12910,7 +12910,7 @@
         <v>45854</v>
       </c>
       <c r="E217" t="n">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F217" t="b">
         <v>0</v>
@@ -12936,7 +12936,7 @@
         <v>45856</v>
       </c>
       <c r="E218" t="n">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="F218" t="b">
         <v>0</v>
@@ -12962,7 +12962,7 @@
         <v>45862</v>
       </c>
       <c r="E219" t="n">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="F219" t="b">
         <v>0</v>
@@ -12988,7 +12988,7 @@
         <v>45863</v>
       </c>
       <c r="E220" t="n">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F220" t="b">
         <v>0</v>
@@ -13014,7 +13014,7 @@
         <v>45873</v>
       </c>
       <c r="E221" t="n">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="F221" t="b">
         <v>0</v>
@@ -13040,7 +13040,7 @@
         <v>45877</v>
       </c>
       <c r="E222" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="F222" t="b">
         <v>0</v>
@@ -13066,7 +13066,7 @@
         <v>45898</v>
       </c>
       <c r="E223" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="F223" t="b">
         <v>0</v>
@@ -13092,7 +13092,7 @@
         <v>45919</v>
       </c>
       <c r="E224" t="n">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F224" t="b">
         <v>0</v>
@@ -13118,7 +13118,7 @@
         <v>45928</v>
       </c>
       <c r="E225" t="n">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="F225" t="b">
         <v>0</v>
@@ -13144,7 +13144,7 @@
         <v>45950</v>
       </c>
       <c r="E226" t="n">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="F226" t="b">
         <v>0</v>
@@ -13170,7 +13170,7 @@
         <v>45957</v>
       </c>
       <c r="E227" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="F227" t="b">
         <v>0</v>
@@ -13196,7 +13196,7 @@
         <v>45961</v>
       </c>
       <c r="E228" t="n">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F228" t="b">
         <v>0</v>
@@ -13222,7 +13222,7 @@
         <v>45962</v>
       </c>
       <c r="E229" t="n">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F229" t="b">
         <v>0</v>
@@ -13248,7 +13248,7 @@
         <v>45963</v>
       </c>
       <c r="E230" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="F230" t="b">
         <v>0</v>
@@ -13274,7 +13274,7 @@
         <v>45969</v>
       </c>
       <c r="E231" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="F231" t="b">
         <v>0</v>
@@ -13283,24 +13283,24 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>D203791</t>
+          <t>D205216</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Clinic_222</t>
+          <t>Clinic_923</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
         <v>45973</v>
       </c>
       <c r="E232" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F232" t="b">
         <v>0</v>
@@ -13309,24 +13309,24 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>D205216</t>
+          <t>D203791</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Clinic_923</t>
+          <t>Clinic_222</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D233" s="1" t="n">
         <v>45973</v>
       </c>
       <c r="E233" t="n">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="F233" t="b">
         <v>0</v>
@@ -13352,7 +13352,7 @@
         <v>45986</v>
       </c>
       <c r="E234" t="n">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="F234" t="b">
         <v>0</v>
@@ -13378,7 +13378,7 @@
         <v>45991</v>
       </c>
       <c r="E235" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="F235" t="b">
         <v>0</v>
@@ -13404,7 +13404,7 @@
         <v>46004</v>
       </c>
       <c r="E236" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F236" t="b">
         <v>0</v>
@@ -13430,7 +13430,7 @@
         <v>46008</v>
       </c>
       <c r="E237" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="F237" t="b">
         <v>0</v>
@@ -13456,7 +13456,7 @@
         <v>46013</v>
       </c>
       <c r="E238" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F238" t="b">
         <v>0</v>
@@ -13482,7 +13482,7 @@
         <v>46016</v>
       </c>
       <c r="E239" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F239" t="b">
         <v>0</v>
@@ -13508,7 +13508,7 @@
         <v>46017</v>
       </c>
       <c r="E240" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F240" t="b">
         <v>0</v>
@@ -13534,7 +13534,7 @@
         <v>46021</v>
       </c>
       <c r="E241" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F241" t="b">
         <v>0</v>
@@ -13560,7 +13560,7 @@
         <v>46022</v>
       </c>
       <c r="E242" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F242" t="b">
         <v>0</v>
@@ -13569,12 +13569,12 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>D202975</t>
+          <t>D208317</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Clinic_704</t>
+          <t>Clinic_356</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13586,7 +13586,7 @@
         <v>46025</v>
       </c>
       <c r="E243" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F243" t="b">
         <v>0</v>
@@ -13595,12 +13595,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>D208317</t>
+          <t>D202975</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Clinic_356</t>
+          <t>Clinic_704</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13612,7 +13612,7 @@
         <v>46025</v>
       </c>
       <c r="E244" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F244" t="b">
         <v>0</v>
@@ -13638,7 +13638,7 @@
         <v>46039</v>
       </c>
       <c r="E245" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="F245" t="b">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>46043</v>
       </c>
       <c r="E246" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="F246" t="b">
         <v>0</v>
@@ -13690,7 +13690,7 @@
         <v>46050</v>
       </c>
       <c r="E247" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="F247" t="b">
         <v>0</v>
@@ -13716,7 +13716,7 @@
         <v>46057</v>
       </c>
       <c r="E248" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F248" t="b">
         <v>0</v>
@@ -13742,7 +13742,7 @@
         <v>46070</v>
       </c>
       <c r="E249" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F249" t="b">
         <v>0</v>
@@ -13768,7 +13768,7 @@
         <v>46072</v>
       </c>
       <c r="E250" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F250" t="b">
         <v>0</v>
@@ -13794,7 +13794,7 @@
         <v>46073</v>
       </c>
       <c r="E251" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F251" t="b">
         <v>0</v>
@@ -13820,7 +13820,7 @@
         <v>46077</v>
       </c>
       <c r="E252" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="F252" t="b">
         <v>0</v>
@@ -13846,7 +13846,7 @@
         <v>46078</v>
       </c>
       <c r="E253" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="F253" t="b">
         <v>0</v>
@@ -13872,7 +13872,7 @@
         <v>46082</v>
       </c>
       <c r="E254" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="F254" t="b">
         <v>0</v>
@@ -13898,7 +13898,7 @@
         <v>46087</v>
       </c>
       <c r="E255" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="F255" t="b">
         <v>0</v>
@@ -13924,7 +13924,7 @@
         <v>46103</v>
       </c>
       <c r="E256" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F256" t="b">
         <v>0</v>
@@ -13950,7 +13950,7 @@
         <v>46125</v>
       </c>
       <c r="E257" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F257" t="b">
         <v>0</v>
@@ -13959,41 +13959,43 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>D204940</t>
+          <t>D206683</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Clinic_440</t>
+          <t>Clinic_644</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>MDX-100</t>
+        </is>
+      </c>
+      <c r="D258" s="1" t="n">
+        <v>46131</v>
+      </c>
       <c r="E258" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="F258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>D201980</t>
+          <t>D204940</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Clinic_923</t>
+          <t>Clinic_440</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
@@ -14007,17 +14009,17 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>D203300</t>
+          <t>D201980</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Clinic_423</t>
+          <t>Clinic_923</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D260" t="inlineStr"/>
@@ -14031,17 +14033,17 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>D208557</t>
+          <t>D203300</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Clinic_405</t>
+          <t>Clinic_423</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -14055,17 +14057,17 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>D203802</t>
+          <t>D208557</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Clinic_529</t>
+          <t>Clinic_405</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -14079,17 +14081,17 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>D200337</t>
+          <t>D203802</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Clinic_873</t>
+          <t>Clinic_529</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -14103,17 +14105,17 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>D200966</t>
+          <t>D200337</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Clinic_962</t>
+          <t>Clinic_873</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D264" t="inlineStr"/>
@@ -14127,12 +14129,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>D203271</t>
+          <t>D200966</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Clinic_238</t>
+          <t>Clinic_962</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -14151,12 +14153,12 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>D207607</t>
+          <t>D203271</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Clinic_824</t>
+          <t>Clinic_238</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -14175,12 +14177,12 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>D206248</t>
+          <t>D207607</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Clinic_962</t>
+          <t>Clinic_824</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -14199,17 +14201,17 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>D205585</t>
+          <t>D206248</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Clinic_930</t>
+          <t>Clinic_962</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D268" t="inlineStr"/>
@@ -14223,17 +14225,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>D208350</t>
+          <t>D205585</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Clinic_856</t>
+          <t>Clinic_930</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D269" t="inlineStr"/>
@@ -14247,17 +14249,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>D209975</t>
+          <t>D208350</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Clinic_343</t>
+          <t>Clinic_856</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D270" t="inlineStr"/>
@@ -14271,17 +14273,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>D204110</t>
+          <t>D209975</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Clinic_867</t>
+          <t>Clinic_343</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -14295,17 +14297,17 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>D207903</t>
+          <t>D204110</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Clinic_599</t>
+          <t>Clinic_867</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D272" t="inlineStr"/>
@@ -14319,17 +14321,17 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>D205897</t>
+          <t>D207903</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Clinic_269</t>
+          <t>Clinic_599</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D273" t="inlineStr"/>
@@ -14343,17 +14345,17 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>D206545</t>
+          <t>D205897</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Clinic_242</t>
+          <t>Clinic_269</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr"/>
@@ -14367,17 +14369,17 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>D207008</t>
+          <t>D206545</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Clinic_305</t>
+          <t>Clinic_242</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D275" t="inlineStr"/>
@@ -14391,17 +14393,17 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>D205436</t>
+          <t>D207008</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Clinic_500</t>
+          <t>Clinic_305</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -14415,17 +14417,17 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>D203124</t>
+          <t>D205436</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Clinic_912</t>
+          <t>Clinic_500</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D277" t="inlineStr"/>
@@ -14439,17 +14441,17 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>D203831</t>
+          <t>D203124</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Clinic_941</t>
+          <t>Clinic_912</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D278" t="inlineStr"/>
@@ -14463,17 +14465,17 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>D205480</t>
+          <t>D203831</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>Clinic_294</t>
+          <t>Clinic_941</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D279" t="inlineStr"/>
@@ -14487,17 +14489,17 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>D206855</t>
+          <t>D205480</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>Clinic_580</t>
+          <t>Clinic_294</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D280" t="inlineStr"/>
@@ -14511,17 +14513,17 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>D201018</t>
+          <t>D206855</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>Clinic_832</t>
+          <t>Clinic_580</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D281" t="inlineStr"/>
@@ -14535,17 +14537,17 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>D206822</t>
+          <t>D201018</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>Clinic_944</t>
+          <t>Clinic_832</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D282" t="inlineStr"/>
@@ -14559,17 +14561,17 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>D208196</t>
+          <t>D206822</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Clinic_385</t>
+          <t>Clinic_944</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D283" t="inlineStr"/>
@@ -14583,17 +14585,17 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>D200418</t>
+          <t>D208196</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>Clinic_952</t>
+          <t>Clinic_385</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D284" t="inlineStr"/>
@@ -14607,17 +14609,17 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>D200880</t>
+          <t>D200418</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>Clinic_728</t>
+          <t>Clinic_952</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D285" t="inlineStr"/>
@@ -14631,17 +14633,17 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>D202860</t>
+          <t>D200880</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Clinic_669</t>
+          <t>Clinic_728</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D286" t="inlineStr"/>
@@ -14655,17 +14657,17 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>D208975</t>
+          <t>D202860</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>Clinic_824</t>
+          <t>Clinic_669</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D287" t="inlineStr"/>
@@ -14679,17 +14681,17 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>D209525</t>
+          <t>D208975</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>Clinic_616</t>
+          <t>Clinic_824</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D288" t="inlineStr"/>
@@ -14703,17 +14705,17 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>D205019</t>
+          <t>D209525</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>Clinic_325</t>
+          <t>Clinic_616</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D289" t="inlineStr"/>
@@ -14727,17 +14729,17 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>D209492</t>
+          <t>D205019</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>Clinic_320</t>
+          <t>Clinic_325</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D290" t="inlineStr"/>
@@ -14751,17 +14753,17 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>D209631</t>
+          <t>D209492</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>Clinic_930</t>
+          <t>Clinic_320</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D291" t="inlineStr"/>
@@ -14775,17 +14777,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>D208337</t>
+          <t>D209631</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>Clinic_230</t>
+          <t>Clinic_930</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D292" t="inlineStr"/>
@@ -14799,17 +14801,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>D209790</t>
+          <t>D208337</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>Clinic_265</t>
+          <t>Clinic_230</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D293" t="inlineStr"/>
@@ -14823,17 +14825,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>D205066</t>
+          <t>D209790</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Clinic_509</t>
+          <t>Clinic_265</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D294" t="inlineStr"/>
@@ -14847,17 +14849,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>D201485</t>
+          <t>D205066</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Clinic_911</t>
+          <t>Clinic_509</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D295" t="inlineStr"/>
@@ -14871,17 +14873,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>D209080</t>
+          <t>D201485</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>Clinic_496</t>
+          <t>Clinic_911</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D296" t="inlineStr"/>
@@ -14895,17 +14897,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>D209480</t>
+          <t>D209080</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>Clinic_526</t>
+          <t>Clinic_496</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D297" t="inlineStr"/>
@@ -14919,17 +14921,17 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>D202492</t>
+          <t>D209480</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Clinic_947</t>
+          <t>Clinic_526</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D298" t="inlineStr"/>
@@ -14943,17 +14945,17 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>D203103</t>
+          <t>D202492</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>Clinic_884</t>
+          <t>Clinic_947</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D299" t="inlineStr"/>
@@ -14967,12 +14969,12 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>D206486</t>
+          <t>D203103</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>Clinic_348</t>
+          <t>Clinic_884</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -14991,17 +14993,17 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>D209593</t>
+          <t>D206486</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Clinic_246</t>
+          <t>Clinic_348</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D301" t="inlineStr"/>
@@ -15015,17 +15017,17 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>D201285</t>
+          <t>D209593</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>Clinic_312</t>
+          <t>Clinic_246</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D302" t="inlineStr"/>
@@ -15039,17 +15041,17 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>D203024</t>
+          <t>D201285</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Clinic_424</t>
+          <t>Clinic_312</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D303" t="inlineStr"/>
@@ -15063,17 +15065,17 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>D201317</t>
+          <t>D203024</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>Clinic_356</t>
+          <t>Clinic_424</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
@@ -15087,17 +15089,17 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>D200555</t>
+          <t>D201317</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>Clinic_712</t>
+          <t>Clinic_356</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
@@ -15111,17 +15113,17 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>D209301</t>
+          <t>D200555</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Clinic_782</t>
+          <t>Clinic_712</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
@@ -15135,12 +15137,12 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>D207507</t>
+          <t>D209301</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Clinic_235</t>
+          <t>Clinic_782</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -15159,17 +15161,17 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>D209039</t>
+          <t>D207507</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Clinic_986</t>
+          <t>Clinic_235</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
@@ -15183,17 +15185,17 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>D207129</t>
+          <t>D209039</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>Clinic_761</t>
+          <t>Clinic_986</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
@@ -15207,17 +15209,17 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>D207516</t>
+          <t>D207129</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>Clinic_873</t>
+          <t>Clinic_761</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
@@ -15231,17 +15233,17 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>D206828</t>
+          <t>D207516</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Clinic_584</t>
+          <t>Clinic_873</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
@@ -15255,17 +15257,17 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>D208462</t>
+          <t>D206828</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Clinic_408</t>
+          <t>Clinic_584</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
@@ -15279,17 +15281,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>D204709</t>
+          <t>D208462</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Clinic_954</t>
+          <t>Clinic_408</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D313" t="inlineStr"/>
@@ -15303,17 +15305,17 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>D208517</t>
+          <t>D204709</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Clinic_328</t>
+          <t>Clinic_954</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
@@ -15327,17 +15329,17 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>D208922</t>
+          <t>D208517</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>Clinic_797</t>
+          <t>Clinic_328</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
@@ -15351,17 +15353,17 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>D200229</t>
+          <t>D208922</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>Clinic_210</t>
+          <t>Clinic_797</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
@@ -15375,17 +15377,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>D208833</t>
+          <t>D200229</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Clinic_249</t>
+          <t>Clinic_210</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
@@ -15399,12 +15401,12 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>D207272</t>
+          <t>D208833</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>Clinic_865</t>
+          <t>Clinic_249</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -15423,17 +15425,17 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>D209161</t>
+          <t>D207272</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>Clinic_284</t>
+          <t>Clinic_865</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
@@ -15447,17 +15449,17 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>D208117</t>
+          <t>D209161</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>Clinic_951</t>
+          <t>Clinic_284</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
@@ -15471,17 +15473,17 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>D206176</t>
+          <t>D208117</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>Clinic_696</t>
+          <t>Clinic_951</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
@@ -15495,17 +15497,17 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>D200806</t>
+          <t>D206176</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Clinic_763</t>
+          <t>Clinic_696</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D322" t="inlineStr"/>
@@ -15519,17 +15521,17 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>D201907</t>
+          <t>D200806</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Clinic_704</t>
+          <t>Clinic_763</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D323" t="inlineStr"/>
@@ -15543,17 +15545,17 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>D205021</t>
+          <t>D201907</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>Clinic_773</t>
+          <t>Clinic_704</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D324" t="inlineStr"/>
@@ -15567,17 +15569,17 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>D209192</t>
+          <t>D205021</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>Clinic_821</t>
+          <t>Clinic_773</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D325" t="inlineStr"/>
@@ -15591,17 +15593,17 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>D209282</t>
+          <t>D209192</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>Clinic_310</t>
+          <t>Clinic_821</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D326" t="inlineStr"/>
@@ -15615,17 +15617,17 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>D201283</t>
+          <t>D209282</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Clinic_326</t>
+          <t>Clinic_310</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D327" t="inlineStr"/>
@@ -15639,17 +15641,17 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>D202833</t>
+          <t>D201283</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Clinic_928</t>
+          <t>Clinic_326</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D328" t="inlineStr"/>
@@ -15663,17 +15665,17 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>D201985</t>
+          <t>D202833</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>Clinic_768</t>
+          <t>Clinic_928</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D329" t="inlineStr"/>
@@ -15687,17 +15689,17 @@
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>D206859</t>
+          <t>D201985</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>Clinic_275</t>
+          <t>Clinic_768</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D330" t="inlineStr"/>
@@ -15711,17 +15713,17 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>D200167</t>
+          <t>D206859</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>Clinic_872</t>
+          <t>Clinic_275</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D331" t="inlineStr"/>
@@ -15735,17 +15737,17 @@
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>D208941</t>
+          <t>D200167</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>Clinic_827</t>
+          <t>Clinic_872</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D332" t="inlineStr"/>
@@ -15759,17 +15761,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>D206022</t>
+          <t>D208941</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>Clinic_462</t>
+          <t>Clinic_827</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D333" t="inlineStr"/>
@@ -15783,17 +15785,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>D207976</t>
+          <t>D206022</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>Clinic_683</t>
+          <t>Clinic_462</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D334" t="inlineStr"/>
@@ -15807,17 +15809,17 @@
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>D200537</t>
+          <t>D207976</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>Clinic_831</t>
+          <t>Clinic_683</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D335" t="inlineStr"/>
@@ -15831,12 +15833,12 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>D200421</t>
+          <t>D200537</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>Clinic_220</t>
+          <t>Clinic_831</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -15855,17 +15857,17 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>D200368</t>
+          <t>D200421</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Clinic_938</t>
+          <t>Clinic_220</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D337" t="inlineStr"/>
@@ -15879,17 +15881,17 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>D209127</t>
+          <t>D200368</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Clinic_906</t>
+          <t>Clinic_938</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D338" t="inlineStr"/>
@@ -15903,17 +15905,17 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>D200878</t>
+          <t>D209127</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Clinic_596</t>
+          <t>Clinic_906</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D339" t="inlineStr"/>
@@ -15927,17 +15929,17 @@
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>D201172</t>
+          <t>D200878</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Clinic_718</t>
+          <t>Clinic_596</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D340" t="inlineStr"/>
@@ -15951,17 +15953,17 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>D204206</t>
+          <t>D201172</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Clinic_874</t>
+          <t>Clinic_718</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D341" t="inlineStr"/>
@@ -15975,12 +15977,12 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>D208942</t>
+          <t>D204206</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Clinic_881</t>
+          <t>Clinic_874</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -15999,12 +16001,12 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>D200827</t>
+          <t>D208942</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Clinic_884</t>
+          <t>Clinic_881</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -16023,12 +16025,12 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>D205479</t>
+          <t>D200827</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Clinic_944</t>
+          <t>Clinic_884</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -16047,17 +16049,17 @@
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>D202158</t>
+          <t>D205479</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>Clinic_690</t>
+          <t>Clinic_944</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D345" t="inlineStr"/>
@@ -16071,17 +16073,17 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>D207967</t>
+          <t>D202158</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Clinic_608</t>
+          <t>Clinic_690</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D346" t="inlineStr"/>
@@ -16095,17 +16097,17 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>D200442</t>
+          <t>D207967</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>Clinic_571</t>
+          <t>Clinic_608</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D347" t="inlineStr"/>
@@ -16119,12 +16121,12 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>D206543</t>
+          <t>D200442</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>Clinic_611</t>
+          <t>Clinic_571</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -16143,17 +16145,17 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>D208149</t>
+          <t>D206543</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>Clinic_855</t>
+          <t>Clinic_611</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D349" t="inlineStr"/>
@@ -16167,17 +16169,17 @@
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>D201140</t>
+          <t>D208149</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>Clinic_973</t>
+          <t>Clinic_855</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D350" t="inlineStr"/>
@@ -16191,17 +16193,17 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>D202825</t>
+          <t>D201140</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Clinic_927</t>
+          <t>Clinic_973</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
@@ -16215,17 +16217,17 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>D207523</t>
+          <t>D202825</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Clinic_645</t>
+          <t>Clinic_927</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D352" t="inlineStr"/>
@@ -16239,17 +16241,17 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>D209397</t>
+          <t>D207523</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>Clinic_289</t>
+          <t>Clinic_645</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D353" t="inlineStr"/>
@@ -16263,12 +16265,12 @@
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>D207165</t>
+          <t>D209397</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Clinic_876</t>
+          <t>Clinic_289</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -16287,12 +16289,12 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>D202334</t>
+          <t>D207165</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Clinic_995</t>
+          <t>Clinic_876</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -16311,17 +16313,17 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>D204478</t>
+          <t>D202334</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Clinic_764</t>
+          <t>Clinic_995</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D356" t="inlineStr"/>
@@ -16335,12 +16337,12 @@
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>D200583</t>
+          <t>D204478</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Clinic_717</t>
+          <t>Clinic_764</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -16359,12 +16361,12 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>D205349</t>
+          <t>D200583</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Clinic_815</t>
+          <t>Clinic_717</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -16383,17 +16385,17 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>D201154</t>
+          <t>D205349</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Clinic_558</t>
+          <t>Clinic_815</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D359" t="inlineStr"/>
@@ -16407,17 +16409,17 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>D203079</t>
+          <t>D201154</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Clinic_863</t>
+          <t>Clinic_558</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D360" t="inlineStr"/>
@@ -16431,17 +16433,17 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>D205258</t>
+          <t>D203079</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Clinic_232</t>
+          <t>Clinic_863</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D361" t="inlineStr"/>
@@ -16455,17 +16457,17 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>D205209</t>
+          <t>D205258</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Clinic_911</t>
+          <t>Clinic_232</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D362" t="inlineStr"/>
@@ -16479,17 +16481,17 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>D205465</t>
+          <t>D205209</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Clinic_958</t>
+          <t>Clinic_911</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D363" t="inlineStr"/>
@@ -16503,17 +16505,17 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>D208647</t>
+          <t>D205465</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Clinic_885</t>
+          <t>Clinic_958</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D364" t="inlineStr"/>
@@ -16527,17 +16529,17 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>D203007</t>
+          <t>D208647</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Clinic_296</t>
+          <t>Clinic_885</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D365" t="inlineStr"/>
@@ -16551,17 +16553,17 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>D208672</t>
+          <t>D203007</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>Clinic_811</t>
+          <t>Clinic_296</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D366" t="inlineStr"/>
@@ -16575,12 +16577,12 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>D209305</t>
+          <t>D208672</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>Clinic_515</t>
+          <t>Clinic_811</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -16599,17 +16601,17 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>D201207</t>
+          <t>D209305</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Clinic_431</t>
+          <t>Clinic_515</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D368" t="inlineStr"/>
@@ -16623,17 +16625,17 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>D202055</t>
+          <t>D201207</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Clinic_308</t>
+          <t>Clinic_431</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D369" t="inlineStr"/>
@@ -16647,17 +16649,17 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>D200871</t>
+          <t>D202055</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>Clinic_305</t>
+          <t>Clinic_308</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D370" t="inlineStr"/>
@@ -16671,17 +16673,17 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>D200204</t>
+          <t>D200871</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>Clinic_525</t>
+          <t>Clinic_305</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D371" t="inlineStr"/>
@@ -16695,17 +16697,17 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>D203008</t>
+          <t>D200204</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Clinic_712</t>
+          <t>Clinic_525</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -16719,17 +16721,17 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>D208344</t>
+          <t>D203008</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Clinic_813</t>
+          <t>Clinic_712</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -16743,17 +16745,17 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>D203710</t>
+          <t>D208344</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Clinic_330</t>
+          <t>Clinic_813</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D374" t="inlineStr"/>
@@ -16767,17 +16769,17 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>D205721</t>
+          <t>D203710</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Clinic_806</t>
+          <t>Clinic_330</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -16791,17 +16793,17 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>D200371</t>
+          <t>D205721</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Clinic_439</t>
+          <t>Clinic_806</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -16815,17 +16817,17 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>D201484</t>
+          <t>D200371</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>Clinic_714</t>
+          <t>Clinic_439</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -16839,17 +16841,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>D204672</t>
+          <t>D201484</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>Clinic_314</t>
+          <t>Clinic_714</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -16863,17 +16865,17 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>D204572</t>
+          <t>D204672</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Clinic_551</t>
+          <t>Clinic_314</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D379" t="inlineStr"/>
@@ -16887,17 +16889,17 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>D202505</t>
+          <t>D204572</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Clinic_375</t>
+          <t>Clinic_551</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -16911,17 +16913,17 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>D201294</t>
+          <t>D202505</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>Clinic_768</t>
+          <t>Clinic_375</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -16935,17 +16937,17 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>D207393</t>
+          <t>D201294</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Clinic_234</t>
+          <t>Clinic_768</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -16959,17 +16961,17 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>D208822</t>
+          <t>D207393</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Clinic_587</t>
+          <t>Clinic_234</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -16983,17 +16985,17 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>D202499</t>
+          <t>D208822</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>Clinic_661</t>
+          <t>Clinic_587</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -17007,17 +17009,17 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>D207914</t>
+          <t>D202499</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Clinic_926</t>
+          <t>Clinic_661</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D385" t="inlineStr"/>
@@ -17031,17 +17033,17 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>D207932</t>
+          <t>D207914</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Clinic_594</t>
+          <t>Clinic_926</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D386" t="inlineStr"/>
@@ -17055,17 +17057,17 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>D209171</t>
+          <t>D207932</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Clinic_246</t>
+          <t>Clinic_594</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
@@ -17079,17 +17081,17 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>D205295</t>
+          <t>D209171</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Clinic_854</t>
+          <t>Clinic_246</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D388" t="inlineStr"/>
@@ -17103,17 +17105,17 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>D205813</t>
+          <t>D205295</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Clinic_527</t>
+          <t>Clinic_854</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
@@ -17127,17 +17129,17 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>D207937</t>
+          <t>D205813</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Clinic_693</t>
+          <t>Clinic_527</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D390" t="inlineStr"/>
@@ -17151,17 +17153,17 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>D208262</t>
+          <t>D207937</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>Clinic_803</t>
+          <t>Clinic_693</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D391" t="inlineStr"/>
@@ -17175,17 +17177,17 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>D208689</t>
+          <t>D208262</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Clinic_282</t>
+          <t>Clinic_803</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D392" t="inlineStr"/>
@@ -17199,17 +17201,17 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>D203522</t>
+          <t>D208689</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Clinic_721</t>
+          <t>Clinic_282</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
@@ -17223,17 +17225,17 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>D209655</t>
+          <t>D203522</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Clinic_805</t>
+          <t>Clinic_721</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
@@ -17247,17 +17249,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>D206265</t>
+          <t>D209655</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Clinic_509</t>
+          <t>Clinic_805</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
@@ -17271,17 +17273,17 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>D200133</t>
+          <t>D206265</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Clinic_471</t>
+          <t>Clinic_509</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D396" t="inlineStr"/>
@@ -17295,17 +17297,17 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>D200887</t>
+          <t>D200133</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Clinic_702</t>
+          <t>Clinic_471</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
@@ -17319,17 +17321,17 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>D203138</t>
+          <t>D200887</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Clinic_434</t>
+          <t>Clinic_702</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
@@ -17343,17 +17345,17 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>D209685</t>
+          <t>D203138</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Clinic_634</t>
+          <t>Clinic_434</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
@@ -17367,17 +17369,17 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>D204483</t>
+          <t>D209685</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Clinic_829</t>
+          <t>Clinic_634</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
@@ -17391,12 +17393,12 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>D207263</t>
+          <t>D204483</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Clinic_276</t>
+          <t>Clinic_829</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -17415,17 +17417,17 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>D202970</t>
+          <t>D207263</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Clinic_685</t>
+          <t>Clinic_276</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
@@ -17439,17 +17441,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>D209687</t>
+          <t>D202970</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Clinic_264</t>
+          <t>Clinic_685</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
@@ -17463,17 +17465,17 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>D200265</t>
+          <t>D209687</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Clinic_899</t>
+          <t>Clinic_264</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
@@ -17487,12 +17489,12 @@
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>D201251</t>
+          <t>D200265</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Clinic_725</t>
+          <t>Clinic_899</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -17511,17 +17513,17 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>D200066</t>
+          <t>D201251</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Clinic_953</t>
+          <t>Clinic_725</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
@@ -17535,12 +17537,12 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>D204018</t>
+          <t>D200066</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Clinic_897</t>
+          <t>Clinic_953</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -17559,12 +17561,12 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>D205268</t>
+          <t>D204018</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Clinic_209</t>
+          <t>Clinic_897</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -17583,17 +17585,17 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>D201188</t>
+          <t>D205268</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Clinic_292</t>
+          <t>Clinic_209</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D409" t="inlineStr"/>
@@ -17607,17 +17609,17 @@
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>D205761</t>
+          <t>D201188</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Clinic_859</t>
+          <t>Clinic_292</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
@@ -17631,17 +17633,17 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>D205896</t>
+          <t>D205761</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Clinic_632</t>
+          <t>Clinic_859</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
@@ -17655,12 +17657,12 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>D200490</t>
+          <t>D205896</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>Clinic_821</t>
+          <t>Clinic_632</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -17679,17 +17681,17 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>D201495</t>
+          <t>D200490</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Clinic_643</t>
+          <t>Clinic_821</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D413" t="inlineStr"/>
@@ -17703,17 +17705,17 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>D208379</t>
+          <t>D201495</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Clinic_852</t>
+          <t>Clinic_643</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D414" t="inlineStr"/>
@@ -17727,17 +17729,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>D201296</t>
+          <t>D208379</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Clinic_970</t>
+          <t>Clinic_852</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D415" t="inlineStr"/>
@@ -17751,17 +17753,17 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>D206006</t>
+          <t>D201296</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>Clinic_600</t>
+          <t>Clinic_970</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D416" t="inlineStr"/>
@@ -17775,17 +17777,17 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>D206996</t>
+          <t>D206006</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>Clinic_994</t>
+          <t>Clinic_600</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D417" t="inlineStr"/>
@@ -17799,17 +17801,17 @@
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>D203915</t>
+          <t>D206996</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>Clinic_869</t>
+          <t>Clinic_994</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D418" t="inlineStr"/>
@@ -17823,17 +17825,17 @@
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>D200521</t>
+          <t>D203915</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Clinic_799</t>
+          <t>Clinic_869</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D419" t="inlineStr"/>
@@ -17847,17 +17849,17 @@
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>D209895</t>
+          <t>D200521</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Clinic_514</t>
+          <t>Clinic_799</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D420" t="inlineStr"/>
@@ -17871,12 +17873,12 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>D205047</t>
+          <t>D209895</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>Clinic_488</t>
+          <t>Clinic_514</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -17895,17 +17897,17 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>D203721</t>
+          <t>D205047</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>Clinic_751</t>
+          <t>Clinic_488</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D422" t="inlineStr"/>
@@ -17919,17 +17921,17 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>D200474</t>
+          <t>D203721</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Clinic_778</t>
+          <t>Clinic_751</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D423" t="inlineStr"/>
@@ -17943,17 +17945,17 @@
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>D200292</t>
+          <t>D200474</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Clinic_779</t>
+          <t>Clinic_778</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D424" t="inlineStr"/>
@@ -17967,17 +17969,17 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>D200495</t>
+          <t>D200292</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>Clinic_591</t>
+          <t>Clinic_779</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D425" t="inlineStr"/>
@@ -17991,17 +17993,17 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>D203844</t>
+          <t>D200495</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Clinic_579</t>
+          <t>Clinic_591</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D426" t="inlineStr"/>
@@ -18015,17 +18017,17 @@
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>D202968</t>
+          <t>D203844</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Clinic_914</t>
+          <t>Clinic_579</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D427" t="inlineStr"/>
@@ -18039,17 +18041,17 @@
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>D207232</t>
+          <t>D202968</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>Clinic_365</t>
+          <t>Clinic_914</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D428" t="inlineStr"/>
@@ -18063,17 +18065,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>D209321</t>
+          <t>D207232</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>Clinic_374</t>
+          <t>Clinic_365</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D429" t="inlineStr"/>
@@ -18087,17 +18089,17 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>D205123</t>
+          <t>D209321</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>Clinic_839</t>
+          <t>Clinic_374</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D430" t="inlineStr"/>
@@ -18111,17 +18113,17 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>D202260</t>
+          <t>D205123</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Clinic_644</t>
+          <t>Clinic_839</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D431" t="inlineStr"/>
@@ -18135,17 +18137,17 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>D204918</t>
+          <t>D202260</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Clinic_377</t>
+          <t>Clinic_644</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D432" t="inlineStr"/>
@@ -18159,17 +18161,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>D204629</t>
+          <t>D204918</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Clinic_900</t>
+          <t>Clinic_377</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D433" t="inlineStr"/>
@@ -18183,17 +18185,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>D208562</t>
+          <t>D204629</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Clinic_654</t>
+          <t>Clinic_900</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D434" t="inlineStr"/>
@@ -18207,17 +18209,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>D202990</t>
+          <t>D208562</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Clinic_372</t>
+          <t>Clinic_654</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D435" t="inlineStr"/>
@@ -18231,12 +18233,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>D207804</t>
+          <t>D202990</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Clinic_313</t>
+          <t>Clinic_372</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -18255,17 +18257,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>D208622</t>
+          <t>D207804</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Clinic_346</t>
+          <t>Clinic_313</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D437" t="inlineStr"/>
@@ -18279,17 +18281,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>D207433</t>
+          <t>D208622</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Clinic_530</t>
+          <t>Clinic_346</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D438" t="inlineStr"/>
@@ -18303,17 +18305,17 @@
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>D208276</t>
+          <t>D207433</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Clinic_234</t>
+          <t>Clinic_530</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D439" t="inlineStr"/>
@@ -18327,17 +18329,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>D204575</t>
+          <t>D208276</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Clinic_328</t>
+          <t>Clinic_234</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D440" t="inlineStr"/>
@@ -18351,12 +18353,12 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>D203537</t>
+          <t>D204575</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Clinic_545</t>
+          <t>Clinic_328</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -18375,17 +18377,17 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>D201808</t>
+          <t>D203537</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>Clinic_257</t>
+          <t>Clinic_545</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D442" t="inlineStr"/>
@@ -18399,17 +18401,17 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>D209495</t>
+          <t>D201808</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Clinic_217</t>
+          <t>Clinic_257</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>UltiScan V2</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D443" t="inlineStr"/>
@@ -18423,17 +18425,17 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>D208017</t>
+          <t>D209495</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Clinic_215</t>
+          <t>Clinic_217</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>MDX-100</t>
+          <t>UltiScan V2</t>
         </is>
       </c>
       <c r="D444" t="inlineStr"/>
@@ -18447,17 +18449,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>D200457</t>
+          <t>D208017</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Clinic_289</t>
+          <t>Clinic_215</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-100</t>
         </is>
       </c>
       <c r="D445" t="inlineStr"/>
@@ -18471,17 +18473,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>D202547</t>
+          <t>D200457</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Clinic_573</t>
+          <t>Clinic_289</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D446" t="inlineStr"/>
@@ -18495,12 +18497,12 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>D205103</t>
+          <t>D202547</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>Clinic_488</t>
+          <t>Clinic_573</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -18519,17 +18521,17 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>D202952</t>
+          <t>D205103</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>Clinic_862</t>
+          <t>Clinic_488</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D448" t="inlineStr"/>
@@ -18543,17 +18545,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>D201538</t>
+          <t>D202952</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Clinic_616</t>
+          <t>Clinic_862</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>SafeScan Pro</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D449" t="inlineStr"/>
@@ -18567,17 +18569,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>D204075</t>
+          <t>D201538</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>Clinic_590</t>
+          <t>Clinic_616</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>SafeScan Pro</t>
         </is>
       </c>
       <c r="D450" t="inlineStr"/>
@@ -18591,17 +18593,17 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>D205309</t>
+          <t>D204075</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>Clinic_238</t>
+          <t>Clinic_590</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D451" t="inlineStr"/>
@@ -18615,17 +18617,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>D205542</t>
+          <t>D205309</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Clinic_692</t>
+          <t>Clinic_238</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>UltraDiag-3</t>
         </is>
       </c>
       <c r="D452" t="inlineStr"/>
@@ -18639,17 +18641,17 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>D202369</t>
+          <t>D205542</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Clinic_560</t>
+          <t>Clinic_692</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>NeoScan X</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D453" t="inlineStr"/>
@@ -18663,17 +18665,17 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>D208995</t>
+          <t>D202369</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Clinic_765</t>
+          <t>Clinic_560</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>MDX-200</t>
+          <t>NeoScan X</t>
         </is>
       </c>
       <c r="D454" t="inlineStr"/>
@@ -18687,17 +18689,17 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>D205675</t>
+          <t>D208995</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Clinic_473</t>
+          <t>Clinic_765</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>UltraDiag-3</t>
+          <t>MDX-200</t>
         </is>
       </c>
       <c r="D455" t="inlineStr"/>
@@ -18711,27 +18713,25 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>D206683</t>
+          <t>D205675</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Clinic_644</t>
+          <t>Clinic_473</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>MDX-100</t>
-        </is>
-      </c>
-      <c r="D456" s="1" t="n">
-        <v>46131</v>
-      </c>
+          <t>UltraDiag-3</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
       <c r="E456" t="n">
         <v>-1</v>
       </c>
       <c r="F456" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="457">
@@ -31714,7 +31714,7 @@
         <v>46147</v>
       </c>
       <c r="E997" t="n">
-        <v>-17</v>
+        <v>-12</v>
       </c>
       <c r="F997" t="b">
         <v>0</v>
@@ -31740,7 +31740,7 @@
         <v>46184</v>
       </c>
       <c r="E998" t="n">
-        <v>-54</v>
+        <v>-49</v>
       </c>
       <c r="F998" t="b">
         <v>0</v>
@@ -31766,7 +31766,7 @@
         <v>46199</v>
       </c>
       <c r="E999" t="n">
-        <v>-69</v>
+        <v>-64</v>
       </c>
       <c r="F999" t="b">
         <v>0</v>
@@ -31792,7 +31792,7 @@
         <v>46240</v>
       </c>
       <c r="E1000" t="n">
-        <v>-110</v>
+        <v>-105</v>
       </c>
       <c r="F1000" t="b">
         <v>0</v>
@@ -31818,7 +31818,7 @@
         <v>46248</v>
       </c>
       <c r="E1001" t="n">
-        <v>-118</v>
+        <v>-113</v>
       </c>
       <c r="F1001" t="b">
         <v>0</v>
@@ -31844,7 +31844,7 @@
         <v>46304</v>
       </c>
       <c r="E1002" t="n">
-        <v>-174</v>
+        <v>-169</v>
       </c>
       <c r="F1002" t="b">
         <v>0</v>
